--- a/Pruebas calificadas/COLEGIO NUEVA ROMA-1103_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO NUEVA ROMA-1103_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -4357,7 +4297,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -4610,7 +4546,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -4863,7 +4795,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -5116,7 +5044,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -5369,7 +5293,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -5622,7 +5542,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5783,11 +5703,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -5795,7 +5711,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6032,11 +5948,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -6044,7 +5956,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6285,11 +6197,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -6297,7 +6205,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6538,11 +6446,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -6550,7 +6454,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6791,11 +6695,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -6803,7 +6703,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7044,11 +6944,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -7056,7 +6952,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7297,11 +7193,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -7309,7 +7201,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7550,11 +7442,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -7562,7 +7450,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7799,11 +7687,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -7811,7 +7695,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8044,11 +7928,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -8056,7 +7936,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8297,11 +8177,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -8309,7 +8185,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8550,11 +8426,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -8562,7 +8434,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8803,11 +8675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -8815,7 +8683,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9056,11 +8924,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -9068,7 +8932,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9309,11 +9173,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -9321,7 +9181,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9558,11 +9418,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -9570,7 +9426,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9811,11 +9667,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -9823,7 +9675,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10064,11 +9916,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -10076,7 +9924,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10317,11 +10165,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -10329,7 +10173,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10570,11 +10414,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -10582,7 +10422,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10823,11 +10663,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -10835,7 +10671,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11076,11 +10912,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -11088,7 +10920,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11329,11 +11161,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -11341,7 +11169,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11582,11 +11410,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -11594,7 +11418,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11835,11 +11659,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -11847,7 +11667,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12052,11 +11872,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -12064,7 +11880,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12305,11 +12121,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -12317,7 +12129,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12558,11 +12370,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -12570,7 +12378,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12811,11 +12619,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -12823,7 +12627,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13060,11 +12864,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -13072,7 +12872,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13313,11 +13113,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -13325,7 +13121,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13566,11 +13362,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -13578,7 +13370,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13819,11 +13611,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -13831,7 +13619,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14068,11 +13856,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -14080,7 +13864,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14321,11 +14105,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -14333,7 +14113,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14574,11 +14354,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001098817</t>
@@ -14586,7 +14362,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO NUEVA ROMA (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
